--- a/Firmware/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Rtos/Rtos_Validation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,7 +687,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>کد بازبینی + host test</t>
@@ -698,7 +697,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -761,7 +759,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -772,7 +769,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -835,7 +831,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -846,7 +841,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -909,7 +903,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -920,7 +913,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -983,14 +975,11 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1053,14 +1042,11 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1123,7 +1109,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
@@ -1134,7 +1119,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1197,7 +1181,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
@@ -1208,7 +1191,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1271,14 +1253,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1341,17 +1320,86 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RT-011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>هر ۷ محل CheckIn/PollKick واچ‌داگ در پنج تسک را بگرد: همه باید زمان را از تبدیل rtos_time بگیرند (func__Rtos_TicksToMilliseconds)، نه تیک خام کرنل</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>004fbf1</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
